--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -477,10 +477,20 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Fuentes (original)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Links fuentes (original)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Clasificación preexistencia BO</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Justificación preexistencia BO</t>
         </is>
@@ -489,175 +499,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Proyecto de Licuefacción de Gas Natural (FLNG - Southern Energy)</t>
+          <t>Ampliación del Tramo I del Gasoducto Perito Francisco Pascasio Moreno (GPM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Instalación de una planta flotante de licuefacción de gas natural para obtener Gas Natural Licuado (GNL)</t>
+          <t>Construcción, financiamiento y Operación y Mantenimiento (O&amp;M) de la infraestructura involucrada para generar una capacidad incremental de catorce millones de metros cúbicos por día (14 MMm³/d) al Tramo I del Gasoducto Francisco Pascasio Moren</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TGS (Argentina)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Transportadora de Gas del Sur S.A. Sucursal Dedicada 1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30-71881250-6</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Neuquén; Buenos Aires</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Desde Tratayén, Neuquén, hasta Salliqueló, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>550</v>
+      </c>
+      <c r="M2">
+        <v>513</v>
+      </c>
+      <c r="N2">
+        <v>7535</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="P2" s="2">
+        <v>45957</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>46142</v>
+      </c>
+      <c r="R2" s="2">
+        <v>46154</v>
+      </c>
+      <c r="S2" s="2">
+        <v>46154</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Res. 676/2026</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/341877/20260513</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 676/2026; MECON</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Res. 676/2026, Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pan American Energy (PAE) (Argentina); YPF S.A. (Argentina); Pampa Energía (Argentina); Harbour Energy (Reino Unido); Golar LNG (Noruega)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Southern Energy S.A.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>30-71858062-1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Petróleo y Gas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Licuefacción</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Patagonia</t>
-        </is>
-      </c>
-      <c r="L2">
-        <v>15156</v>
-      </c>
-      <c r="M2">
-        <v>2825</v>
-      </c>
-      <c r="N2">
-        <v>836</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="P2" s="2">
-        <v>45617</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>45775</v>
-      </c>
-      <c r="R2" s="2">
-        <v>45776</v>
-      </c>
-      <c r="S2" s="2">
-        <v>45776</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Res. 559/2025</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/324772/20250505</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Res. 559/2025; Globaris; MECON</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>La resolución para la planta de Licuefacción de Gas Natural (FLNG) describe la instalación de una planta flotante de GNL y conexión a gasoductos, sin señalar etapas previas ni ampliaciones.</t>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>La resolución describe la “Ampliación del Tramo I” del Gasoducto Perito Francisco Moreno, instalando compresoras para aumentar la capacidad de un gasoducto ya existente, lo cual prueba que el proyecto es una ampliación de un activo preexistente.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vaca Muerta Oleoducto Sur (VMOS)</t>
+          <t>Diablillos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
+          <t>Comprende actividades destinadas a la factibilidad, desarrollo, ejecución y operación del yacimiento de oro y plata “Diablillos”, integrado por quince (15) concesiones mineras contiguas y superpuestas en la zona limítrofe entre las provincias de Salta y Catamarca</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina) · Pan American Energy (PAE) (Argentina) · Vista Energy (Argentina) · Pampa Energía (Argentina) · Pluspetrol (Argentina) · Chevron (Estados Unidos) · Tecpetrol S.A. (Argentina) · Shell (Reino Unido) · Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>AbraSilver Resource Corp. (Canadá)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VMOS S.A.</t>
+          <t>Pacific Rim Mining Corporation Argentina S.A.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30-718713354</t>
+          <t>30-67305977-1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Salta; Catamarca</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L3">
-        <v>2900</v>
+        <v>764</v>
       </c>
       <c r="M3">
-        <v>2486</v>
+        <v>482</v>
       </c>
       <c r="N3">
-        <v>3108</v>
+        <v>2013</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -665,57 +680,62 @@
         </is>
       </c>
       <c r="P3" s="2">
-        <v>45611</v>
+        <v>45981</v>
       </c>
       <c r="Q3" s="2">
-        <v>45722</v>
+        <v>46080</v>
       </c>
       <c r="R3" s="2">
-        <v>45736</v>
+        <v>46149</v>
       </c>
       <c r="S3" s="2">
-        <v>45736</v>
+        <v>46149</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Res. 302/2025</t>
+          <t>Res. 562/2026</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/322830/20250321</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/341756/20260511</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Res. 302/2025; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 562/2026; MECON</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Res. 562/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>La resolución del oleoducto VMOS describe la construcción de un oleoducto de 437 km y terminales de exportación para incrementar la capacidad de transporte de petróleo; no se mencionan ampliaciones de un oleoducto existente.</t>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>La resolución para el proyecto Diablillos detalla la construcción de una planta de procesamiento y obras asociadas para un yacimiento de oro y plata sin mencionar expansiones ni proyectos previos.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Proyecto Los Azules</t>
+          <t>Carbonatos Profundos (DCP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
+          <t>Exploración de las concesiones mineras Gualcamayo 1 y Gualcamayo 2 y la determinación de la factibilidad del yacimiento de reservas minerales de oro y plata denominado “Carbonatos Profundos”, y la construcción, puesta en marcha y operación de la planta de tratamiento de dichos minerales extraídos del Proyecto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -725,17 +745,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>McEwen Copper Inc. (Canadá)</t>
+          <t>Aisa Group (Canadá)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Andes Corporación Minera SA (ACM)</t>
+          <t>Minas Argentinas S.A.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30-70952278-3</t>
+          <t>30-71915462-6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -745,7 +765,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -759,13 +779,13 @@
         </is>
       </c>
       <c r="L4">
-        <v>2672.171</v>
+        <v>665</v>
       </c>
       <c r="M4">
-        <v>2354</v>
+        <v>520</v>
       </c>
       <c r="N4">
-        <v>7391</v>
+        <v>4500</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -773,107 +793,112 @@
         </is>
       </c>
       <c r="P4" s="2">
-        <v>45849</v>
+        <v>45814</v>
       </c>
       <c r="Q4" s="2">
-        <v>45925</v>
+        <v>45988</v>
       </c>
       <c r="R4" s="2">
-        <v>45943</v>
+        <v>46035</v>
       </c>
       <c r="S4" s="2">
-        <v>45943</v>
+        <v>46035</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Res. 1553/2025</t>
+          <t>Res. 6/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/332807/20251014</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/337468/20260115</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Res. 1553/2025; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 6/2026; MECON</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ambiguo</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>La norma del Proyecto Los Azules menciona que el objetivo es completar el desarrollo (factibilidad y permisos) y construir la mina y planta, lo que sugiere que hay estudios y permisos previos; sin embargo, no se identifica claramente la existencia de una operación activa previa.</t>
+          <t>Res. 6/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>La norma del proyecto Carbonatos Profundos describe la exploración de las concesiones Gualcamayo 1 y 2 y la construcción de una planta de tratamiento, sin referencias a fases previas o ampliaciones.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Proyecto Rincón</t>
+          <t>Parque Eólico Olavarría</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Extracción directa de litio, nanofiltración y pretratamiento de salmuera que posibilitarán la extracción de litio sin la necesidad de concentración previa en piletas de evaporación, lo que reducirá significativamente el impacto ambiental y la alteración del paisaje, a la vez que también permitirá reducir la generación de residuos y la necesidad de reactivos químicos en el proceso.</t>
+          <t>Instalación de un parque eólico de ciento ochenta (180) megavatios (180 MW) ubicado en la localidad de Olavarría, provincia de Buenos Aires, que también involucra la construcción de una nueva estación transformadora (ET) de treinta y tres a ciento treinta y dos kilovoltios (33/132 Kv) simple barra con dos transformadores de ciento veinte megavoltiamperios (120 MVA) y tres (3) campos, una línea de alta tensión (LAT) de ciento treinta y dos kilovoltios (132 Kv) de aproximadamente veinticinco kilómetros (25 km) de longitud que vinculará el parque eólico con la ET Olavarría -propiedad de TRANSBA SA-, y las obras de ampliación del sistema de transporte que incluirán la repotenciación de los capacitores series en la ET Olavarría y la ampliación de banco de capacitores shunt en la ET Ezeiza</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rio Tinto (Reino Unido)</t>
+          <t>PCR S.A. (Argentina); Acindar (ArcelorMittal) (Argentina)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rincón Mining Pty Ltd.</t>
+          <t>Generación Eléctrica Argentina Renovable I SA (GEAR)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-70708643-9</t>
+          <t>30-71592816-3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Eólico</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="L5">
-        <v>2744</v>
+        <v>276</v>
       </c>
       <c r="M5">
-        <v>2299</v>
+        <v>255</v>
       </c>
       <c r="N5">
-        <v>1985</v>
+        <v>165</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -881,57 +906,62 @@
         </is>
       </c>
       <c r="P5" s="2">
-        <v>45713</v>
+        <v>45656</v>
       </c>
       <c r="Q5" s="2">
-        <v>45796</v>
+        <v>45863</v>
       </c>
       <c r="R5" s="2">
-        <v>45807</v>
+        <v>45895</v>
       </c>
       <c r="S5" s="2">
-        <v>45807</v>
+        <v>45895</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Res. 735/2025</t>
+          <t>Res. 1254/2025</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/326364/20250603</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330400/20250827</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Res. 735/2025; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1254/2025; MECON</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>La resolución del Proyecto Rincón detalla que la producción provendrá tanto de la planta Rincón 3000, con capacidad de 3.000 t de LCE, como de la construcción y operación de dos plantas “Rincón Full Potential” de 25.000 t cada una, mostrando que el proyecto amplía una planta existente.</t>
+          <t>Res. 1254/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>La resolución del Parque Eólico Olavarría describe la instalación de un nuevo parque eólico de 180 MW y obras de conexión eléctrica. Aunque se mencionan ampliaciones de la red de transporte, estas se refieren al sistema eléctrico y no evidencian un parque eólico preexistente.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PSJ Cobre Mendocino</t>
+          <t>Parque Solar El Quemado y Anexos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Desarrollo, extracción y procesamiento de minerales sulfurados de cobre con recuperación de oro como subproducto del yacimiento “San Jorge”, y contempla la construcción y operación de una mina a cielo abierto y una planta concentradora basada en técnicas de flotación convencional</t>
+          <t>Parque solar fotovoltaico ubicado en la localidad de Jocolí del departamento Las Heras de la provincia de Mendoza, el cual tendrá una capacidad instalada por un total de trescientos cinco megavatios (305 MW) a desarrollarse en dos (2) etapas y proveerá energía</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -941,27 +971,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zonda Metals GmBH (Suiza); Alberdi Energy (Argentina)</t>
+          <t>Luz de Campo S.A.; YPF Luz (Argentina)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Minera San Jorge SA</t>
+          <t>Luz del Campo S.A.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30-69228382-8</t>
+          <t>30-71765521-0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Energio Solar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -975,13 +1005,13 @@
         </is>
       </c>
       <c r="L6">
-        <v>891</v>
+        <v>211</v>
       </c>
       <c r="M6">
-        <v>613.4299999999999</v>
+        <v>212</v>
       </c>
       <c r="N6">
-        <v>6300</v>
+        <v>384</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -989,165 +1019,175 @@
         </is>
       </c>
       <c r="P6" s="2">
-        <v>45967</v>
+        <v>45590</v>
       </c>
       <c r="Q6" s="2">
-        <v>46155</v>
+        <v>45642</v>
       </c>
       <c r="R6" s="2">
-        <v>46168</v>
+        <v>45664</v>
       </c>
       <c r="S6" s="2">
-        <v>46168</v>
+        <v>45664</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Res. 801/2026</t>
+          <t>Res. 1/2025</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342483/20260528</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/319374/20250108</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Res. 801/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1/2025; MECON</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Res. 1/2025, Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>La norma del proyecto PSJ Cobre Mendocino expone la construcción y operación de una nueva mina a cielo abierto y planta concentradora en el yacimiento San Jorge, sin referencias a fases anteriores ni instalaciones preexistentes.</t>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>La resolución del Parque Solar El Quemado y Anexos indica la construcción de un parque solar fotovoltaico de 305 MW desarrollado en dos etapas; no hay menciones a instalaciones solares previas ni a ampliaciones de un proyecto existente.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carbonatos Profundos (DCP)</t>
+          <t>Proyecto de Licuefacción de Gas Natural (FLNG - Southern Energy)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Exploración de las concesiones mineras Gualcamayo 1 y Gualcamayo 2 y la determinación de la factibilidad del yacimiento de reservas minerales de oro y plata denominado “Carbonatos Profundos”, y la construcción, puesta en marcha y operación de la planta de tratamiento de dichos minerales extraídos del Proyecto</t>
+          <t>Instalación de una planta flotante de licuefacción de gas natural para obtener Gas Natural Licuado (GNL)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina); YPF S.A. (Argentina); Pampa Energía (Argentina); Harbour Energy (Reino Unido); Golar LNG (Noruega)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Southern Energy S.A.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30-71858062-1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Licuefacción</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="L7">
+        <v>15156</v>
+      </c>
+      <c r="M7">
+        <v>2825</v>
+      </c>
+      <c r="N7">
+        <v>836</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="P7" s="2">
+        <v>45617</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>45775</v>
+      </c>
+      <c r="R7" s="2">
+        <v>45776</v>
+      </c>
+      <c r="S7" s="2">
+        <v>45776</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Res. 559/2025</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/324772/20250505</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 559/2025; MECON</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Res. 559/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Aisa Group (Canadá)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Minas Argentinas S.A.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>30-71915462-6</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Oro y Plata</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Cuyo</t>
-        </is>
-      </c>
-      <c r="L7">
-        <v>665</v>
-      </c>
-      <c r="M7">
-        <v>519.647</v>
-      </c>
-      <c r="N7">
-        <v>4500</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="P7" s="2">
-        <v>45814</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>45988</v>
-      </c>
-      <c r="R7" s="2">
-        <v>46035</v>
-      </c>
-      <c r="S7" s="2">
-        <v>46035</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Res. 6/2026</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/337468/20260115</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Res. 6/2026; Globaris; MECON</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>La norma del proyecto Carbonatos Profundos describe la exploración de las concesiones Gualcamayo 1 y 2 y la construcción de una planta de tratamiento, sin referencias a fases previas o ampliaciones.</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>La resolución para la planta de Licuefacción de Gas Natural (FLNG) describe la instalación de una planta flotante de GNL y conexión a gasoductos, sin señalar etapas previas ni ampliaciones.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ampliación del Tramo I del Gasoducto Perito Francisco Pascasio Moreno (GPM)</t>
+          <t>Proyecto Siderúrgico Argentino Sidersa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Construcción, financiamiento y Operación y Mantenimiento (O&amp;M) de la infraestructura involucrada para generar una capacidad incremental de catorce millones de metros cúbicos por día (14 MMm³/d) al Tramo I del Gasoducto Francisco Pascasio Moren</t>
+          <t>Construcción y puesta en operación de una nueva planta de aceros largos, que incluye tanto la acería como la laminadora continua en tándem, de menores emisiones de dióxido de carbono (CO2) respecto de las tecnologías tradicionales y bajo un modelo de producción de economía circular que permitirá reducir el consumo de recursos naturales y disminuir la huella ambiental a partir del uso de un noventa y nueve coma cinco por ciento (99,5%) de chatarra como materia prima</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1157,47 +1197,47 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TGS (Argentina)</t>
+          <t>Sidersa S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur S.A. Sucursal Dedicada 1</t>
+          <t>Sidersa Acería S.D.E.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30-71881250-6</t>
+          <t>33-71879284-9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Neuquén; Buenos Aires</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Desde Tratayén, Neuquén, hasta Salliqueló, Buenos Aires</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L8">
-        <v>550</v>
+        <v>286</v>
       </c>
       <c r="M8">
-        <v>513.372</v>
+        <v>286</v>
       </c>
       <c r="N8">
-        <v>7535</v>
+        <v>3800</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1205,57 +1245,62 @@
         </is>
       </c>
       <c r="P8" s="2">
-        <v>45957</v>
+        <v>45638</v>
       </c>
       <c r="Q8" s="2">
-        <v>46142</v>
+        <v>45807</v>
       </c>
       <c r="R8" s="2">
-        <v>46154</v>
+        <v>45859</v>
       </c>
       <c r="S8" s="2">
-        <v>46154</v>
+        <v>45859</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Res. 676/2026</t>
+          <t>Res. 1028/2025</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/341877/20260513</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/328690/20250722</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Res. 676/2026, Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1028/2025; MECON</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>La resolución describe la “Ampliación del Tramo I” del Gasoducto Perito Francisco Moreno, instalando compresoras para aumentar la capacidad de un gasoducto ya existente, lo cual prueba que el proyecto es una ampliación de un activo preexistente.</t>
+          <t>Res. 1028/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>El Proyecto Siderúrgico Argentino Sidersa consiste en construir y poner en marcha una nueva planta de acería y laminación de aceros largos; la resolución no indica ampliaciones de plantas existentes.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diablillos</t>
+          <t>PSJ Cobre Mendocino</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comprende actividades destinadas a la factibilidad, desarrollo, ejecución y operación del yacimiento de oro y plata “Diablillos”, integrado por quince (15) concesiones mineras contiguas y superpuestas en la zona limítrofe entre las provincias de Salta y Catamarca</t>
+          <t>Desarrollo, extracción y procesamiento de minerales sulfurados de cobre con recuperación de oro como subproducto del yacimiento “San Jorge”, y contempla la construcción y operación de una mina a cielo abierto y una planta concentradora basada en técnicas de flotación convencional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1265,17 +1310,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AbraSilver Resource Corp. (Canadá)</t>
+          <t>Zonda Metals GmBH (Suiza); Alberdi Energy (Argentina)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pacific Rim Mining Corporation Argentina S.A.</t>
+          <t>Minera San Jorge SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30-67305977-1</t>
+          <t>30-69228382-8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1285,27 +1330,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Salta; Catamarca</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="L9">
-        <v>764</v>
+        <v>891</v>
       </c>
       <c r="M9">
-        <v>481.7</v>
+        <v>613</v>
       </c>
       <c r="N9">
-        <v>2013</v>
+        <v>6300</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1313,77 +1358,82 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <v>45981</v>
+        <v>45967</v>
       </c>
       <c r="Q9" s="2">
-        <v>46080</v>
+        <v>46155</v>
       </c>
       <c r="R9" s="2">
-        <v>46149</v>
+        <v>46168</v>
       </c>
       <c r="S9" s="2">
-        <v>46149</v>
+        <v>46168</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Res. 562/2026</t>
+          <t>Res. 801/2026</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/341756/20260511</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342483/20260528</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Res. 562/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 801/2026; MECON</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Res. 801/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>La resolución para el proyecto Diablillos detalla la construcción de una planta de procesamiento y obras asociadas para un yacimiento de oro y plata sin mencionar expansiones ni proyectos previos.</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>La norma del proyecto PSJ Cobre Mendocino expone la construcción y operación de una nueva mina a cielo abierto y planta concentradora en el yacimiento San Jorge, sin referencias a fases anteriores ni instalaciones preexistentes.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ampliación Fases 8 y 9 del Sistema de Lixiviación en Valle de Mina Veladero</t>
+          <t>Proyecto Rincón</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Proyecto de ampliación comprende la construcción, puesta en marcha y operación de nuevas plataformas del sistema de lixiviación en el valle, definido como el sistema de procesamiento de mineral en la mina Veladero donde se apila el material y se irriga con soluciones para lixiviar el oro y la plata de la mina Veladero, denominadas “Fase 8 y Fase 9”, así como la posterior exportación de los metales preciosos (bullion doré, una aleación de oro y plata) contenidos en el mineral</t>
+          <t>Extracción directa de litio, nanofiltración y pretratamiento de salmuera que posibilitarán la extracción de litio sin la necesidad de concentración previa en piletas de evaporación, lo que reducirá significativamente el impacto ambiental y la alteración del paisaje, a la vez que también permitirá reducir la generación de residuos y la necesidad de reactivos químicos en el proceso.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barrick Gold Corporation (Canadá); Shandong Gold (China)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minera Andina del Sol S.R.L. Sucursal Dedicada 1 (“MAS-SD1”)</t>
+          <t>Rincón Mining Pty Ltd.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30-71906943-2</t>
+          <t>30-70708643-9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1393,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L10">
-        <v>436</v>
+        <v>2744</v>
       </c>
       <c r="M10">
-        <v>380.116</v>
+        <v>2299</v>
       </c>
       <c r="N10">
-        <v>1048</v>
+        <v>1985</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1421,57 +1471,62 @@
         </is>
       </c>
       <c r="P10" s="2">
-        <v>45873</v>
+        <v>45713</v>
       </c>
       <c r="Q10" s="2">
-        <v>46050</v>
+        <v>45796</v>
       </c>
       <c r="R10" s="2">
-        <v>46111</v>
+        <v>45807</v>
       </c>
       <c r="S10" s="2">
-        <v>46111</v>
+        <v>45807</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Res. 413/2026</t>
+          <t>Res. 735/2025</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/340249/20260401</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/326364/20250603</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Res. 413/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 735/2025; MECON</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Res. 735/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>La resolución para las Fases 8 y 9 del Sistema de Lixiviación en Valle de Mina Veladero señala que se trata de una ampliación de un proyecto preexistente (Fases 1–7), agregando nuevas fases al sistema de lixiviación.</t>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>La resolución del Proyecto Rincón detalla que la producción provendrá tanto de la planta Rincón 3000, con capacidad de 3.000 t de LCE, como de la construcción y operación de dos plantas “Rincón Full Potential” de 25.000 t cada una, mostrando que el proyecto amplía una planta existente.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Proyecto Siderúrgico Argentino Sidersa</t>
+          <t>Expansión Fase 1B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Construcción y puesta en operación de una nueva planta de aceros largos, que incluye tanto la acería como la laminadora continua en tándem, de menores emisiones de dióxido de carbono (CO2) respecto de las tecnologías tradicionales y bajo un modelo de producción de economía circular que permitirá reducir el consumo de recursos naturales y disminuir la huella ambiental a partir del uso de un noventa y nueve coma cinco por ciento (99,5%) de chatarra como materia prima</t>
+          <t>Construcción de una nueva Planta de Adsorción Selectiva (SA 1B) y una nueva Planta de Carbonato (PC 1B); asimismo, incluye la perforación de pozos de salmuera adicionales, la instalación de estanques, tuberías, servicios públicos y la construcción de edificios auxiliares para apoyar la operación y administración de la nueva producción de carbonato de litio (cf., RE-2025-96020090-APN-SCEYM#MEC), como así también, la construcción de una nueva Planta Compresora de Gas Natural en la localidad de Olacapato, departamento de Los Andes, provincia de Salta, situada dentro del radio de doscientos kilómetros (200 km) del Proyecto, que permitirá ampliar la capacidad de transporte de los gasoductos “La Puna” y “Fénix”, instalaciones asociadas directamente al abastecimiento y transporte de gas natural para la nueva producción del proyecto “Expansión Fase 1B”.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1481,47 +1536,47 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sidersa S.A. (Argentina)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidersa Acería S.D.E.</t>
+          <t>Minera del Altiplano S.A. Sucursal Dedicada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33-71879284-9</t>
+          <t>30-71906845-2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L11">
-        <v>286.278</v>
+        <v>531</v>
       </c>
       <c r="M11">
-        <v>286.278</v>
+        <v>251</v>
       </c>
       <c r="N11">
-        <v>3800</v>
+        <v>1273</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1529,47 +1584,52 @@
         </is>
       </c>
       <c r="P11" s="2">
-        <v>45638</v>
+        <v>45898</v>
       </c>
       <c r="Q11" s="2">
-        <v>45807</v>
+        <v>46106</v>
       </c>
       <c r="R11" s="2">
-        <v>45859</v>
+        <v>46112</v>
       </c>
       <c r="S11" s="2">
-        <v>45859</v>
+        <v>46112</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Res. 1028/2025</t>
+          <t>Res. 431/2026</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/328690/20250722</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/340329/20260406</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Res. 1028/2025; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 431/2026; MECON</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>El Proyecto Siderúrgico Argentino Sidersa consiste en construir y poner en marcha una nueva planta de acería y laminación de aceros largos; la resolución no indica ampliaciones de plantas existentes.</t>
+          <t>Res. 431/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>La resolución del proyecto “Expansión Fase 1B” señala que consiste en la ampliación del proyecto preexistente Fénix para incrementar la capacidad productiva de carbonato de litio en 9.500 t/año.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1623,10 +1683,10 @@
         </is>
       </c>
       <c r="L12">
-        <v>276.9</v>
+        <v>277</v>
       </c>
       <c r="M12">
-        <v>276.9</v>
+        <v>277</v>
       </c>
       <c r="N12">
         <v>9700</v>
@@ -1660,15 +1720,20 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1842/2025; MECON</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>Res. 1842/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>La resolución del Proyecto Terminal Multipropósito Timbúes aprueba la construcción y operación de una nueva terminal portuaria compuesta por tres unidades logístico‑portuarias; la norma no menciona ninguna infraestructura portuaria previa.</t>
         </is>
@@ -1677,125 +1742,130 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Parque Eólico Olavarría</t>
+          <t>Vaca Muerta Oleoducto Sur (VMOS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Instalación de un parque eólico de ciento ochenta (180) megavatios (180 MW) ubicado en la localidad de Olavarría, provincia de Buenos Aires, que también involucra la construcción de una nueva estación transformadora (ET) de treinta y tres a ciento treinta y dos kilovoltios (33/132 Kv) simple barra con dos transformadores de ciento veinte megavoltiamperios (120 MVA) y tres (3) campos, una línea de alta tensión (LAT) de ciento treinta y dos kilovoltios (132 Kv) de aproximadamente veinticinco kilómetros (25 km) de longitud que vinculará el parque eólico con la ET Olavarría -propiedad de TRANSBA SA-, y las obras de ampliación del sistema de transporte que incluirán la repotenciación de los capacitores series en la ET Olavarría y la ampliación de banco de capacitores shunt en la ET Ezeiza</t>
+          <t>Consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>YPF S.A. (Argentina) · Pan American Energy (PAE) (Argentina) · Vista Energy (Argentina) · Pampa Energía (Argentina) · Pluspetrol (Argentina) · Chevron (Estados Unidos) · Tecpetrol S.A. (Argentina) · Shell (Reino Unido) · Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VMOS S.A.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30-718713354</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="L13">
+        <v>2900</v>
+      </c>
+      <c r="M13">
+        <v>2486</v>
+      </c>
+      <c r="N13">
+        <v>3108</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="P13" s="2">
+        <v>45611</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>45722</v>
+      </c>
+      <c r="R13" s="2">
+        <v>45736</v>
+      </c>
+      <c r="S13" s="2">
+        <v>45736</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Res. 302/2025</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/322830/20250321</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 302/2025; MECON</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Res. 302/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PCR S.A. (Argentina); Acindar (ArcelorMittal) (Argentina)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Generación Eléctrica Argentina Renovable I SA (GEAR)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>30-71592816-3</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Energía</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Eólico</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="L13">
-        <v>275.59</v>
-      </c>
-      <c r="M13">
-        <v>255.112</v>
-      </c>
-      <c r="N13">
-        <v>165</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="P13" s="2">
-        <v>45656</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>45863</v>
-      </c>
-      <c r="R13" s="2">
-        <v>45895</v>
-      </c>
-      <c r="S13" s="2">
-        <v>45895</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Res. 1254/2025</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330400/20250827</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Res. 1254/2025; Globaris; MECON</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>La resolución del Parque Eólico Olavarría describe la instalación de un nuevo parque eólico de 180 MW y obras de conexión eléctrica. Aunque se mencionan ampliaciones de la red de transporte, estas se refieren al sistema eléctrico y no evidencian un parque eólico preexistente.</t>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>La resolución del oleoducto VMOS describe la construcción de un oleoducto de 437 km y terminales de exportación para incrementar la capacidad de transporte de petróleo; no se mencionan ampliaciones de un oleoducto existente.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Expansión Fase 1B</t>
+          <t>Ampliación Fases 8 y 9 del Sistema de Lixiviación en Valle de Mina Veladero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Construcción de una nueva Planta de Adsorción Selectiva (SA 1B) y una nueva Planta de Carbonato (PC 1B); asimismo, incluye la perforación de pozos de salmuera adicionales, la instalación de estanques, tuberías, servicios públicos y la construcción de edificios auxiliares para apoyar la operación y administración de la nueva producción de carbonato de litio (cf., RE-2025-96020090-APN-SCEYM#MEC), como así también, la construcción de una nueva Planta Compresora de Gas Natural en la localidad de Olacapato, departamento de Los Andes, provincia de Salta, situada dentro del radio de doscientos kilómetros (200 km) del Proyecto, que permitirá ampliar la capacidad de transporte de los gasoductos “La Puna” y “Fénix”, instalaciones asociadas directamente al abastecimiento y transporte de gas natural para la nueva producción del proyecto “Expansión Fase 1B”.</t>
+          <t>Proyecto de ampliación comprende la construcción, puesta en marcha y operación de nuevas plataformas del sistema de lixiviación en el valle, definido como el sistema de procesamiento de mineral en la mina Veladero donde se apila el material y se irriga con soluciones para lixiviar el oro y la plata de la mina Veladero, denominadas “Fase 8 y Fase 9”, así como la posterior exportación de los metales preciosos (bullion doré, una aleación de oro y plata) contenidos en el mineral</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1805,17 +1875,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rio Tinto (Reino Unido)</t>
+          <t>Barrick Gold Corporation (Canadá); Shandong Gold (China)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Minera del Altiplano S.A. Sucursal Dedicada</t>
+          <t>Minera Andina del Sol S.R.L. Sucursal Dedicada 1 (“MAS-SD1”)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30-71906845-2</t>
+          <t>30-71906943-2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1825,27 +1895,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="L14">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="M14">
-        <v>251.321</v>
+        <v>380</v>
       </c>
       <c r="N14">
-        <v>1273</v>
+        <v>1048</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1853,57 +1923,62 @@
         </is>
       </c>
       <c r="P14" s="2">
-        <v>45898</v>
+        <v>45873</v>
       </c>
       <c r="Q14" s="2">
-        <v>46106</v>
+        <v>46050</v>
       </c>
       <c r="R14" s="2">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="S14" s="2">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Res. 431/2026</t>
+          <t>Res. 413/2026</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/340329/20260406</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/340249/20260401</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Res. 431/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 413/2026; MECON</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Res. 413/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>La resolución del proyecto “Expansión Fase 1B” señala que consiste en la ampliación del proyecto preexistente Fénix para incrementar la capacidad productiva de carbonato de litio en 9.500 t/año.</t>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>La resolución para las Fases 8 y 9 del Sistema de Lixiviación en Valle de Mina Veladero señala que se trata de una ampliación de un proyecto preexistente (Fases 1–7), agregando nuevas fases al sistema de lixiviación.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hombre Muerto Oeste (HMW)</t>
+          <t>Ampliación Caucharí Olaroz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
+          <t>Que conforme surge de la presentación, se trata de la ampliación de un proyecto preexistente denominado Cauchari Olaroz con una capacidad productiva instalada de cuarenta mil toneladas (40.000 t) por año de carbonato de litio equivalente (en adelante LCE).</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1913,17 +1988,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galan Lithium Ltd (Australia)</t>
+          <t>Ganfeng (China); Lithium Argentina (Suiza); JEMSE (Argentina)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galan Litio SA</t>
+          <t>Minera Exar Sucursal Dedicada (“EXARSD”)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30-71899846-4</t>
+          <t>30-71924298-3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1938,7 +2013,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1947,13 +2022,13 @@
         </is>
       </c>
       <c r="L15">
-        <v>292</v>
+        <v>1241</v>
       </c>
       <c r="M15">
-        <v>217.09</v>
+        <v>1167</v>
       </c>
       <c r="N15">
-        <v>670</v>
+        <v>1787</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1961,107 +2036,112 @@
         </is>
       </c>
       <c r="P15" s="2">
-        <v>45594</v>
+        <v>45795</v>
       </c>
       <c r="Q15" s="2">
-        <v>45855</v>
+        <v>46151</v>
       </c>
       <c r="R15" s="2">
-        <v>45896</v>
+        <v>46177</v>
       </c>
       <c r="S15" s="2">
-        <v>45896</v>
+        <v>46177</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Res. 1271/2025</t>
+          <t>Res. 825/2026</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342818/20260605</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Res. 1271/2025; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 825/2026; MECON</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>La resolución del Proyecto Hombre Muerto Oeste (HMW) especifica una nueva producción de 12.000 t/año de carbonato de litio equivalente en la cuenca del Salar del Hombre Muerto; no se mencionan ampliaciones de proyectos previos.</t>
+          <t>Res. 825/2026, Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>La resolución del proyecto “Ampliación Cauchari Olaroz” indica que se trata de la ampliación de un proyecto preexistente de 40.000 t/año de LCE; se construirá infraestructura adicional para incrementar la capacidad en 45.000 t/año.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Parque Solar El Quemado y Anexos</t>
+          <t>Proyecto Rincón de Aranda (RDA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parque solar fotovoltaico ubicado en la localidad de Jocolí del departamento Las Heras de la provincia de Mendoza, el cual tendrá una capacidad instalada por un total de trescientos cinco megavatios (305 MW) a desarrollarse en dos (2) etapas y proveerá energía</t>
+          <t>Consiste en: (i) la explotación de nuevos pozos hidrocarburíferos en el área RDA; (ii) el desarrollo, operación y/o prestación del servicio de tratamiento, procesamiento, almacenamiento y transporte del petróleo, gas natural y agua extraídos por PAMPA ENERGÍA SOCIEDAD ANÓNIMA - SUCURSAL DEDICADA PROYECTO RDA del área RDA y/o prestados a terceros, y la disposición final del agua incluyendo, la construcción y operación de plantas, oleoductos y gasoductos; y en (iii) la exportación y/o comercialización de los hidrocarburos y sus derivados obtenidos de la explotación de los nuevos pozos a desarrollarse en el área RDA.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Luz de Campo S.A.; YPF Luz (Argentina)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luz del Campo S.A.</t>
+          <t>Sucursal Dedicada Midstream RDA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30-71765521-0</t>
+          <t>30-71901911-7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Energio Solar</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="L16">
-        <v>211</v>
+        <v>4522</v>
       </c>
       <c r="M16">
-        <v>211.600072</v>
+        <v>4521</v>
       </c>
       <c r="N16">
-        <v>384</v>
+        <v>1733</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2069,57 +2149,62 @@
         </is>
       </c>
       <c r="P16" s="2">
-        <v>45590</v>
+        <v>46090</v>
       </c>
       <c r="Q16" s="2">
-        <v>45642</v>
+        <v>46198</v>
       </c>
       <c r="R16" s="2">
-        <v>45664</v>
+        <v>46224</v>
       </c>
       <c r="S16" s="2">
-        <v>45664</v>
+        <v>46224</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Res. 1/2025</t>
+          <t>Res. 1025/2026</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/319374/20250108</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Res. 1/2025, Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1025/2026; MECON</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>La resolución del Parque Solar El Quemado y Anexos indica la construcción de un parque solar fotovoltaico de 305 MW desarrollado en dos etapas; no hay menciones a instalaciones solares previas ni a ampliaciones de un proyecto existente.</t>
+          <t>Res. 1025/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Se identifican signos fuertes de preexistencia. El Proyecto Rincón de Aranda no surge con la resolución publicada el 21/07/2026. Antes de esa fecha existían antecedentes societarios, operativos, financieros y ambientales: Pampa Energía adquirió el control total del bloque en 2023; la etapa inicial del plan aprobado se declara iniciada el 08/07/2024; en 2024 ya existían EIAs y audiencias públicas para la CPF, oleoductos y gasoductos asociados; en 2025 la empresa ya informaba inversiones, solicitud RIGI, producción y pozos en operación. Por lo tanto, corresponde clasificarlo como proyecto preexistente al anuncio/aprobación oficial, aunque formalizado y ampliado bajo el RIGI como PEELP.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ampliación Caucharí Olaroz</t>
+          <t>Sal de Oro II</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Que conforme surge de la presentación, se trata de la ampliación de un proyecto preexistente denominado Cauchari Olaroz con una capacidad productiva instalada de cuarenta mil toneladas (40.000 t) por año de carbonato de litio equivalente (en adelante LCE).</t>
+          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2129,17 +2214,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ganfeng (China); Lithium Argentina (Suiza); JEMSE (Argentina)</t>
+          <t>Posco (Corea del Sur)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Minera Exar Sucursal Dedicada (“EXARSD”)</t>
+          <t>Posco Argentina SAU SDE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30-71924298-3</t>
+          <t>30-71922048-3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2154,7 +2239,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Salta; Catamarca</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2163,13 +2248,13 @@
         </is>
       </c>
       <c r="L17">
-        <v>1241</v>
+        <v>547</v>
       </c>
       <c r="M17">
-        <v>1166.677726</v>
+        <v>208</v>
       </c>
       <c r="N17">
-        <v>1787</v>
+        <v>2335</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2177,107 +2262,107 @@
         </is>
       </c>
       <c r="P17" s="2">
-        <v>45795</v>
+        <v>45595</v>
       </c>
       <c r="Q17" s="2">
-        <v>46151</v>
+        <v>46185</v>
       </c>
       <c r="R17" s="2">
-        <v>46177</v>
+        <v>46234</v>
       </c>
       <c r="S17" s="2">
-        <v>46177</v>
+        <v>46234</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Res. 825/2026</t>
+          <t>Res. 1157/2026</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342818/20260605</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Res. 825/2026, Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1157/2026; MECON</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Res. 1157/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>La resolución del proyecto “Ampliación Cauchari Olaroz” indica que se trata de la ampliación de un proyecto preexistente de 40.000 t/año de LCE; se construirá infraestructura adicional para incrementar la capacidad en 45.000 t/año.</t>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Signos fuertes de preexistencia del Proyecto Sal de Oro II. POSCO Holdings aprobó la inversión de la segunda fase en octubre de 2022; en junio de 2023, antes del primer anuncio del RIGI, el Gobierno nacional y la empresa comunicaron el inicio de construcción de una planta de carbonato de litio de 23.000 toneladas anuales; y en abril de 2024 POSCO obtuvo financiamiento por hasta USD 668 millones para esa misma fase. Las coincidencias de empresa, localización, producto, capacidad y etapa indican que se trata sustancialmente del mismo proyecto incorporado posteriormente al régimen.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
+          <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>Zijin Mining (LieX S.A.) (China)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE)</t>
+          <t>LIEX S.A.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>30-71703621-9</t>
+          <t>30-71929244-1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Río Negro; Neuquén</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L18">
-        <v>1300</v>
+        <v>710</v>
       </c>
       <c r="M18">
-        <v>955</v>
+        <v>594</v>
       </c>
       <c r="N18">
-        <v>2489</v>
+        <v>4406</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2285,57 +2370,62 @@
         </is>
       </c>
       <c r="P18" s="2">
-        <v>45950</v>
+        <v>46063</v>
       </c>
       <c r="Q18" s="2">
-        <v>46174</v>
+        <v>46206</v>
       </c>
       <c r="R18" s="2">
-        <v>46198</v>
+        <v>46232</v>
       </c>
       <c r="S18" s="2">
-        <v>46198</v>
+        <v>46232</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Res. 873/2026</t>
+          <t>Res. 1153/2026</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Res. 873/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1153/2026; MECON</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Res. 1153/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>PAE ya informaba en 2024 que el esquema de GNL requería infraestructura adicional: interconexión a gasoductos troncales, estación compresora, gasoducto terrestre hasta la costa, gasoducto submarino y sistema de amarre. También indicaba que PAE y Golar habían firmado en julio de 2024 un acuerdo por 20 años para instalar el buque Hilli Episeyo en Argentina.</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Se identifican signos muy fuertes de preexistencia. El proyecto aprobado bajo RIGI corresponde a LIEX S.A. Sucursal Dedicada en el Salar Tres Quebradas —3Q—, Catamarca. Aunque la Resolución 1153/2026 aprueba una inversión en activos computables por USD 594,136 millones para una planta de 40.000 t/año de carbonato de litio, el proyecto 3Q existía públicamente desde años previos: tuvo evaluación económica preliminar en 2017, estudio de factibilidad en 2021, acuerdo provincial ratificado por ley en 2022, adquisición por Zijin/LIEX en 2022, infraestructura eléctrica asociada tramitada desde 2023–2024 y primera fase en producción desde septiembre de 2025.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Proyecto Rincón de Aranda (RDA)</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consiste en: (i) la explotación de nuevos pozos hidrocarburíferos en el área RDA; (ii) el desarrollo, operación y/o prestación del servicio de tratamiento, procesamiento, almacenamiento y transporte del petróleo, gas natural y agua extraídos por PAMPA ENERGÍA SOCIEDAD ANÓNIMA - SUCURSAL DEDICADA PROYECTO RDA del área RDA y/o prestados a terceros, y la disposición final del agua incluyendo, la construcción y operación de plantas, oleoductos y gasoductos; y en (iii) la exportación y/o comercialización de los hidrocarburos y sus derivados obtenidos de la explotación de los nuevos pozos a desarrollarse en el área RDA.</t>
+          <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2345,47 +2435,47 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>BHP (Australia); Lundin Mining (Canadá)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sucursal Dedicada Midstream RDA</t>
+          <t>Vicuña Argentina S.A.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30-71901911-7</t>
+          <t>33-61913055-9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Cobre, Oro y Plata</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="L19">
-        <v>4522</v>
+        <v>9737</v>
       </c>
       <c r="M19">
-        <v>4521</v>
+        <v>9025</v>
       </c>
       <c r="N19">
-        <v>1733</v>
+        <v>31700</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2393,57 +2483,62 @@
         </is>
       </c>
       <c r="P19" s="2">
-        <v>46090</v>
+        <v>46002</v>
       </c>
       <c r="Q19" s="2">
-        <v>46198</v>
+        <v>46176</v>
       </c>
       <c r="R19" s="2">
-        <v>46224</v>
+        <v>46233</v>
       </c>
       <c r="S19" s="2">
-        <v>46224</v>
+        <v>46233</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Res. 1025/2026</t>
+          <t>Res. 1154/2026</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Res. 1025/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1154/2026; MECON</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Res. 1154/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Se identifican signos fuertes de preexistencia. El Proyecto Rincón de Aranda no surge con la resolución publicada el 21/07/2026. Antes de esa fecha existían antecedentes societarios, operativos, financieros y ambientales: Pampa Energía adquirió el control total del bloque en 2023; la etapa inicial del plan aprobado se declara iniciada el 08/07/2024; en 2024 ya existían EIAs y audiencias públicas para la CPF, oleoductos y gasoductos asociados; en 2025 la empresa ya informaba inversiones, solicitud RIGI, producción y pozos en operación. Por lo tanto, corresponde clasificarlo como proyecto preexistente al anuncio/aprobación oficial, aunque formalizado y ampliado bajo el RIGI como PEELP.</t>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Antes del anuncio inicial del RIGI, Josemaría ya contaba con una factibilidad de noviembre de 2020, una evaluación ambiental aprobada en abril de 2022, ingeniería, adquisición de equipos de larga entrega y USD 276 millones de gastos de capital durante 2023; Filo del Sol también poseía prefactibilidades y exploración avanzada. Estos antecedentes corresponden a los mismos depósitos y, principalmente, a la actual primera etapa basada en Josemaría. Sin embargo, la sociedad conjunta BHP–Lundin se constituyó en enero de 2025, la primera evaluación técnica unificada apareció en febrero de 2026 y la decisión final de inversión continuaba pendiente después de la aprobación.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sal de Oro II</t>
+          <t>Proyecto Los Azules</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+          <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2453,17 +2548,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Posco (Corea del Sur)</t>
+          <t>McEwen Copper Inc. (Canadá)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Posco Argentina SAU SDE</t>
+          <t>Andes Corporación Minera SA (ACM)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30-71922048-3</t>
+          <t>30-70952278-3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2473,27 +2568,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Salta; Catamarca</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="L20">
-        <v>547</v>
+        <v>2672</v>
       </c>
       <c r="M20">
-        <v>207.9364272</v>
+        <v>2354</v>
       </c>
       <c r="N20">
-        <v>2335</v>
+        <v>7391</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2501,102 +2596,112 @@
         </is>
       </c>
       <c r="P20" s="2">
-        <v>45595</v>
+        <v>45849</v>
       </c>
       <c r="Q20" s="2">
-        <v>46185</v>
+        <v>45925</v>
       </c>
       <c r="R20" s="2">
-        <v>46234</v>
+        <v>45943</v>
       </c>
       <c r="S20" s="2">
-        <v>46234</v>
+        <v>45943</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Res. 1157/2026</t>
+          <t>Res. 1553/2025</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/332807/20251014</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Res. 1157/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1553/2025; MECON</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Signos fuertes de preexistencia del Proyecto Sal de Oro II. POSCO Holdings aprobó la inversión de la segunda fase en octubre de 2022; en junio de 2023, antes del primer anuncio del RIGI, el Gobierno nacional y la empresa comunicaron el inicio de construcción de una planta de carbonato de litio de 23.000 toneladas anuales; y en abril de 2024 POSCO obtuvo financiamiento por hasta USD 668 millones para esa misma fase. Las coincidencias de empresa, localización, producto, capacidad y etapa indican que se trata sustancialmente del mismo proyecto incorporado posteriormente al régimen.</t>
+          <t>Res. 1553/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Ambiguo</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>La norma del Proyecto Los Azules menciona que el objetivo es completar el desarrollo (factibilidad y permisos) y construir la mina y planta, lo que sugiere que hay estudios y permisos previos; sin embargo, no se identifica claramente la existencia de una operación activa previa.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
+          <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
+          <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zijin Mining (LieX S.A.) (China)</t>
+          <t>Pan American Energy (PAE) (Argentina)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LIEX S.A.</t>
+          <t>Pan American Energy (PAE)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30-71929244-1</t>
+          <t>30-71703621-9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Río Negro; Neuquén</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="L21">
-        <v>710</v>
+        <v>1300</v>
       </c>
       <c r="M21">
-        <v>594.136</v>
+        <v>955</v>
       </c>
       <c r="N21">
-        <v>4406</v>
+        <v>2489</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2604,77 +2709,82 @@
         </is>
       </c>
       <c r="P21" s="2">
-        <v>46063</v>
+        <v>45950</v>
       </c>
       <c r="Q21" s="2">
-        <v>46206</v>
+        <v>46174</v>
       </c>
       <c r="R21" s="2">
-        <v>46232</v>
+        <v>46198</v>
       </c>
       <c r="S21" s="2">
-        <v>46232</v>
+        <v>46198</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Res. 1153/2026</t>
+          <t>Res. 873/2026</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/343613/20260626</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Res. 1153/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 873/2026; MECON</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Res. 873/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Se identifican signos muy fuertes de preexistencia. El proyecto aprobado bajo RIGI corresponde a LIEX S.A. Sucursal Dedicada en el Salar Tres Quebradas —3Q—, Catamarca. Aunque la Resolución 1153/2026 aprueba una inversión en activos computables por USD 594,136 millones para una planta de 40.000 t/año de carbonato de litio, el proyecto 3Q existía públicamente desde años previos: tuvo evaluación económica preliminar en 2017, estudio de factibilidad en 2021, acuerdo provincial ratificado por ley en 2022, adquisición por Zijin/LIEX en 2022, infraestructura eléctrica asociada tramitada desde 2023–2024 y primera fase en producción desde septiembre de 2025.</t>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>PAE ya informaba en 2024 que el esquema de GNL requería infraestructura adicional: interconexión a gasoductos troncales, estación compresora, gasoducto terrestre hasta la costa, gasoducto submarino y sistema de amarre. También indicaba que PAE y Golar habían firmado en julio de 2024 un acuerdo por 20 años para instalar el buque Hilli Episeyo en Argentina.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Hombre Muerto Oeste (HMW)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
+          <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BHP (Australia); Lundin Mining (Canadá)</t>
+          <t>Galan Lithium Ltd (Australia)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vicuña Argentina S.A.</t>
+          <t>Galan Litio SA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>33-61913055-9</t>
+          <t>30-71899846-4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2684,27 +2794,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cobre, Oro y Plata</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="L22">
-        <v>9737.013999999999</v>
+        <v>292</v>
       </c>
       <c r="M22">
-        <v>9024.732281000001</v>
+        <v>217</v>
       </c>
       <c r="N22">
-        <v>31700</v>
+        <v>670</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2712,40 +2822,45 @@
         </is>
       </c>
       <c r="P22" s="2">
-        <v>46002</v>
+        <v>45594</v>
       </c>
       <c r="Q22" s="2">
-        <v>46176</v>
+        <v>45855</v>
       </c>
       <c r="R22" s="2">
-        <v>46233</v>
+        <v>45896</v>
       </c>
       <c r="S22" s="2">
-        <v>46233</v>
+        <v>45896</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Res. 1154/2026</t>
+          <t>Res. 1271/2025</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330470/20250828</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Res. 1154/2026; Globaris; MECON</t>
+          <t>Globaris [https://app.powerbi.com/view?r=eyJrIjoiNTFjY2E4NTYtOTVlNy00YmFiLWIwYmMtNWZkMjE4OTNhYmRiIiwidCI6IjNlMDUxM2Q2LTY4ZmEtNDE2ZS04ZGUxLTZjNWNkYzMxOWZmYSIsImMiOjR9&amp;pageName=d1ee75596a51a9bde708]; Res. 1271/2025; MECON</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Antes del anuncio inicial del RIGI, Josemaría ya contaba con una factibilidad de noviembre de 2020, una evaluación ambiental aprobada en abril de 2022, ingeniería, adquisición de equipos de larga entrega y USD 276 millones de gastos de capital durante 2023; Filo del Sol también poseía prefactibilidades y exploración avanzada. Estos antecedentes corresponden a los mismos depósitos y, principalmente, a la actual primera etapa basada en Josemaría. Sin embargo, la sociedad conjunta BHP–Lundin se constituyó en enero de 2025, la primera evaluación técnica unificada apareció en febrero de 2026 y la decisión final de inversión continuaba pendiente después de la aprobación.</t>
+          <t>Res. 1271/2025; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>La resolución del Proyecto Hombre Muerto Oeste (HMW) especifica una nueva producción de 12.000 t/año de carbonato de litio equivalente en la cuenca del Salar del Hombre Muerto; no se mencionan ampliaciones de proyectos previos.</t>
         </is>
       </c>
     </row>

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>30-718713354</t>
+          <t>30-71871335-4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">

--- a/downloads/base_interactiva_aprobados.xlsx
+++ b/downloads/base_interactiva_aprobados.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -485,16 +485,6 @@
           <t>Links fuentes (original)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Clasificación preexistencia BO</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Justificación preexistencia BO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -598,16 +588,6 @@
           <t>Res. 676/2026, Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>La resolución describe la “Ampliación del Tramo I” del Gasoducto Perito Francisco Moreno, instalando compresoras para aumentar la capacidad de un gasoducto ya existente, lo cual prueba que el proyecto es una ampliación de un activo preexistente.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -711,16 +691,6 @@
           <t>Res. 562/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>La resolución para el proyecto Diablillos detalla la construcción de una planta de procesamiento y obras asociadas para un yacimiento de oro y plata sin mencionar expansiones ni proyectos previos.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -824,16 +794,6 @@
           <t>Res. 6/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>La norma del proyecto Carbonatos Profundos describe la exploración de las concesiones Gualcamayo 1 y 2 y la construcción de una planta de tratamiento, sin referencias a fases previas o ampliaciones.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -937,16 +897,6 @@
           <t>Res. 1254/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>La resolución del Parque Eólico Olavarría describe la instalación de un nuevo parque eólico de 180 MW y obras de conexión eléctrica. Aunque se mencionan ampliaciones de la red de transporte, estas se refieren al sistema eléctrico y no evidencian un parque eólico preexistente.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1050,16 +1000,6 @@
           <t>Res. 1/2025, Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>La resolución del Parque Solar El Quemado y Anexos indica la construcción de un parque solar fotovoltaico de 305 MW desarrollado en dos etapas; no hay menciones a instalaciones solares previas ni a ampliaciones de un proyecto existente.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1163,16 +1103,6 @@
           <t>Res. 559/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>La resolución para la planta de Licuefacción de Gas Natural (FLNG) describe la instalación de una planta flotante de GNL y conexión a gasoductos, sin señalar etapas previas ni ampliaciones.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1276,16 +1206,6 @@
           <t>Res. 1028/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>El Proyecto Siderúrgico Argentino Sidersa consiste en construir y poner en marcha una nueva planta de acería y laminación de aceros largos; la resolución no indica ampliaciones de plantas existentes.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1389,16 +1309,6 @@
           <t>Res. 801/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>La norma del proyecto PSJ Cobre Mendocino expone la construcción y operación de una nueva mina a cielo abierto y planta concentradora en el yacimiento San Jorge, sin referencias a fases anteriores ni instalaciones preexistentes.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1502,16 +1412,6 @@
           <t>Res. 735/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>La resolución del Proyecto Rincón detalla que la producción provendrá tanto de la planta Rincón 3000, con capacidad de 3.000 t de LCE, como de la construcción y operación de dos plantas “Rincón Full Potential” de 25.000 t cada una, mostrando que el proyecto amplía una planta existente.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1615,16 +1515,6 @@
           <t>Res. 431/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>La resolución del proyecto “Expansión Fase 1B” señala que consiste en la ampliación del proyecto preexistente Fénix para incrementar la capacidad productiva de carbonato de litio en 9.500 t/año.</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1728,16 +1618,6 @@
           <t>Res. 1842/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>La resolución del Proyecto Terminal Multipropósito Timbúes aprueba la construcción y operación de una nueva terminal portuaria compuesta por tres unidades logístico‑portuarias; la norma no menciona ninguna infraestructura portuaria previa.</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1841,16 +1721,6 @@
           <t>Res. 302/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>La resolución del oleoducto VMOS describe la construcción de un oleoducto de 437 km y terminales de exportación para incrementar la capacidad de transporte de petróleo; no se mencionan ampliaciones de un oleoducto existente.</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1954,16 +1824,6 @@
           <t>Res. 413/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>La resolución para las Fases 8 y 9 del Sistema de Lixiviación en Valle de Mina Veladero señala que se trata de una ampliación de un proyecto preexistente (Fases 1–7), agregando nuevas fases al sistema de lixiviación.</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2067,16 +1927,6 @@
           <t>Res. 825/2026, Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>La resolución del proyecto “Ampliación Cauchari Olaroz” indica que se trata de la ampliación de un proyecto preexistente de 40.000 t/año de LCE; se construirá infraestructura adicional para incrementar la capacidad en 45.000 t/año.</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2180,16 +2030,6 @@
           <t>Res. 1025/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Se identifican signos fuertes de preexistencia. El Proyecto Rincón de Aranda no surge con la resolución publicada el 21/07/2026. Antes de esa fecha existían antecedentes societarios, operativos, financieros y ambientales: Pampa Energía adquirió el control total del bloque en 2023; la etapa inicial del plan aprobado se declara iniciada el 08/07/2024; en 2024 ya existían EIAs y audiencias públicas para la CPF, oleoductos y gasoductos asociados; en 2025 la empresa ya informaba inversiones, solicitud RIGI, producción y pozos en operación. Por lo tanto, corresponde clasificarlo como proyecto preexistente al anuncio/aprobación oficial, aunque formalizado y ampliado bajo el RIGI como PEELP.</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2293,16 +2133,6 @@
           <t>Res. 1157/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Signos fuertes de preexistencia del Proyecto Sal de Oro II. POSCO Holdings aprobó la inversión de la segunda fase en octubre de 2022; en junio de 2023, antes del primer anuncio del RIGI, el Gobierno nacional y la empresa comunicaron el inicio de construcción de una planta de carbonato de litio de 23.000 toneladas anuales; y en abril de 2024 POSCO obtuvo financiamiento por hasta USD 668 millones para esa misma fase. Las coincidencias de empresa, localización, producto, capacidad y etapa indican que se trata sustancialmente del mismo proyecto incorporado posteriormente al régimen.</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2401,16 +2231,6 @@
           <t>Res. 1153/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Se identifican signos muy fuertes de preexistencia. El proyecto aprobado bajo RIGI corresponde a LIEX S.A. Sucursal Dedicada en el Salar Tres Quebradas —3Q—, Catamarca. Aunque la Resolución 1153/2026 aprueba una inversión en activos computables por USD 594,136 millones para una planta de 40.000 t/año de carbonato de litio, el proyecto 3Q existía públicamente desde años previos: tuvo evaluación económica preliminar en 2017, estudio de factibilidad en 2021, acuerdo provincial ratificado por ley en 2022, adquisición por Zijin/LIEX en 2022, infraestructura eléctrica asociada tramitada desde 2023–2024 y primera fase en producción desde septiembre de 2025.</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2514,16 +2334,6 @@
           <t>Res. 1154/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Antes del anuncio inicial del RIGI, Josemaría ya contaba con una factibilidad de noviembre de 2020, una evaluación ambiental aprobada en abril de 2022, ingeniería, adquisición de equipos de larga entrega y USD 276 millones de gastos de capital durante 2023; Filo del Sol también poseía prefactibilidades y exploración avanzada. Estos antecedentes corresponden a los mismos depósitos y, principalmente, a la actual primera etapa basada en Josemaría. Sin embargo, la sociedad conjunta BHP–Lundin se constituyó en enero de 2025, la primera evaluación técnica unificada apareció en febrero de 2026 y la decisión final de inversión continuaba pendiente después de la aprobación.</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2627,16 +2437,6 @@
           <t>Res. 1553/2025; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Ambiguo</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>La norma del Proyecto Los Azules menciona que el objetivo es completar el desarrollo (factibilidad y permisos) y construir la mina y planta, lo que sugiere que hay estudios y permisos previos; sin embargo, no se identifica claramente la existencia de una operación activa previa.</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2740,16 +2540,6 @@
           <t>Res. 873/2026; Globaris; MECON</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>PAE ya informaba en 2024 que el esquema de GNL requería infraestructura adicional: interconexión a gasoductos troncales, estación compresora, gasoducto terrestre hasta la costa, gasoducto submarino y sistema de amarre. También indicaba que PAE y Golar habían firmado en julio de 2024 un acuerdo por 20 años para instalar el buque Hilli Episeyo en Argentina.</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2851,16 +2641,6 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>Res. 1271/2025; Globaris; MECON</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>La resolución del Proyecto Hombre Muerto Oeste (HMW) especifica una nueva producción de 12.000 t/año de carbonato de litio equivalente en la cuenca del Salar del Hombre Muerto; no se mencionan ampliaciones de proyectos previos.</t>
         </is>
       </c>
     </row>
